--- a/docs/triton-learning/cards/triton-lesson-08-grouped-gemm-technical-qa.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-08-grouped-gemm-technical-qa.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -41,21 +41,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：grouped 只发射一次，也不补齐：所有问题的块合成一份任务，小问题的块填进大问题留下的空档。代价是 kernel 要在设备上自己找任务，而且整组只能共用一套块大小。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：逐个调用浪费的是闲着的 SM 和一次次的发射开销，补齐浪费的是算零的乘加；grouped 只发射一次、也不补齐，把所有问题的块合成一份任务，小问题的块填进大问题留下的空档。
 • [T#B#逐个调用]：同一个 CUDA 流里的 kernel 按提交顺序串行执行。小问题的块数比 SM 少时，这次调用里大部分 SM 闲着，后面的问题也不能提前开始；每次发射还有一笔与矩阵大小无关的固定开销。
-• [T#B#补齐]：batched 接口要求形状相同，只能把小矩阵补零到最大的形状。补的零不影响结果，但照样要算：边长 1024、512、256、128 的四个方阵补齐后，约 71% 的乘加在算零。
-• [T#B#grouped 的代价]：每个 CTA 要扫描问题表才能找到自己的块；调度只均分块数，各问题 K 不同时工作量不均衡。
+• [T#B#补齐]：batched 接口要求形状相同，只能把小矩阵补零到最大的形状。补的零不影响结果，但照样要算：边长 1024、512、256、128 的四个方阵补齐到 1024 后，约 71% 的乘加在算零。
+• [T#B#grouped 的代价]：共三项：每个 CTA 要在设备上扫描问题表，才能找到自己的块；整组只能共用一套块大小；调度只均分块数，各问题 K 不同时工作量不均衡。
 [T#B,!c47f17#边界]：它适合数量多、规模小、K 相近的问题；问题很少、每个都大到能占满所有 SM 时，逐个调用就够了。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">串行的流让 SM 闲置；补齐在算零；grouped 要在设备上找任务</t>
+          <t xml:space="preserve">逐个调用闲置 SM、多次发射；补齐在算零；grouped 要扫描、共用块大小、只均分块数</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 串行的流让 SM 闲置；补齐在算零；grouped 要在设备上找任务</t>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 开课、术语与举例方式</t>
         </is>
       </c>
     </row>
@@ -67,12 +67,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：把每个矩阵的首地址当成 64 位整数存进设备上的张量，kernel 运行时读出整数再转成指针；尺寸和行步长也各存一张表。
-• [T#B#主机侧]：地址表是 int64 的 \[G\]，每项是 tensor.data_ptr()；尺寸表和行步长表是 int32 的 \[G, 3\]，按行展平。行步长就是 stride(0)，行内步长被假定为 1。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：把每个矩阵的首地址当成 64 位整数存进设备上的张量，kernel 运行时读出整数再转成指针；尺寸和行步长也各存一张表。一个张量进了表就只剩一个整数，它的元素类型、对齐和生命周期信息都随之丢失。
+• [T#B#主机侧]：地址表是 int64 的 \[G\]，每项是 tensor.data_ptr()；尺寸表和行步长表是 \[G, 3\]，按行展平。行步长就是 stride(0)，行内步长被假定为 1。
 • [T#B#kernel 侧]：tl.load 读出整数后 .to(tl.pointer_type(tl.float16))，相当于 C 里从 int64_t table\[G\] 取值再强转成 half*。
-• [T#B#丢掉的类型]：指针的元素类型写死在 kernel 里。传入 fp32 的矩阵不会报错，只是把内存按 fp16 解读。
-• [T#B#丢掉的对齐]：张量直接当参数传入时，Triton 在发射时按首地址是否为 16 的倍数做特化；从表里读出的地址没有这一步，对齐只能靠 kernel 里写保证。
-[T#B,!c47f17#边界]：地址表不持有原张量的引用，原张量被释放后地址就悬空；类型、对齐和生命周期都只能由包装函数来保证。</t>
+• [T#B#丢掉的信息]：类型：指针的元素类型写死在 kernel 里，传入别的 dtype 不会被发现；对齐：编译器不知道读出的地址是不是 16 的倍数；生命周期：表不持有原张量的引用，原张量释放后地址就悬空。
+[T#B,!c47f17#边界]：这些信息只能由包装函数在建表之前检查和保证。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -82,24 +81,24 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · data_ptr 存进 int64 表再转成指针；丢类型、丢对齐、不管生命周期</t>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 主机侧打包：地址表与偏移表</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MoE 层里，按专家排好的 token 堆成一个矩阵 X，每个专家的行数不同。PyTorch 2.13 的 grouped_mm(X, W, offs) 用一张偏移表描述各组，Triton 教程的 grouped GEMM 用每组一个地址的地址表。两种表是什么关系？它们分别由谁、在哪里生成，这为什么重要？</t>
+          <t xml:space="preserve">MoE 层里，按专家排好的 token 堆成一个矩阵 X，每个专家的行数不同。PyTorch 2.13 的 grouped_mm(X, W, offs) 用一张偏移表 offs 描述各组，Triton 教程的 grouped GEMM 用每组一个地址的地址表。两种表是什么关系，这层关系为什么让 PyTorch 不必把各组的行数读回主机？</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：偏移表是地址表的特例：各组首尾相接放在同一个张量里时，第 g 组的地址 = 基地址 + 起始行 × 每行字节数。到 kernel 这一层两边用的是同一种表，差别在表由谁、在哪里生成。
-• [T#B#PyTorch]：offs 是设备上的张量。快速路径先在设备上跑一个小 kernel，从 offs 算出每组的地址和行数，全程不把行数读回主机。
-• [T#B#教程]：包装函数在主机上逐个读矩阵的地址、形状和步长，拼成列表再拷到设备，前提是主机已经知道每组的行数。
-• [T#B#为什么重要]：每个专家收到多少 token 是 GPU 上的路由算出来的。主机要知道它就得读回，读回会让主机等 GPU 把排队的工作全部做完。
-• [T#B#能表达的尺寸]：偏移表一次只有一个维度参差；地址表里每个问题的三个维度都可以不同。
-[T#B,!c47f17#边界]：PyTorch 2.13 的快速路径只在 sm_90 或 sm_100、且输入输出都是 bf16 时启用；其余情况退回为把 offs 拷回主机、逐组调用普通矩阵乘。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：偏移表是地址表的特例：各组首尾相接放在同一个张量里，第 g 组的地址 = 基地址 + 起始行 × 每行字节数。地址表因此可以在设备上直接从 offs 算出来，行数不必回到主机。
+• [T#B#例子]：3 个专家、X 为 \[768, 1024\] 的 fp16、offs=\[256, 384, 768\]：三组 A 的地址是 X 的首地址加 0、524288、786432 字节，和教程包装函数从三个切片得到的地址表完全一样。
+• [T#B#PyTorch]：offs 是设备上的张量。快速路径先在设备上跑一个小 kernel，从 offs 算出每组的地址，全程不读回，源码注释是 “fast path, no d2h sync needed”；不满足快速路径条件时，回退路径会把 offs 拷回主机。
+• [T#B#教程]：包装函数在主机上读形状、拼列表再建表，前提是主机已经知道每组的行数；这是包装函数的写法，不是 kernel 的限制。
+• [T#B#为什么重要]：每个专家收到多少 token 是 GPU 上的路由算出来的。主机要知道就得读回，读回会让主机等 GPU 把排队的工作全部做完，即一次同步。
+[T#B,!c47f17#边界]：偏移表一次只能让一个维度参差，其余两维由堆叠的权重统一规定；地址表里每个问题的三个维度都可以不同。</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -109,14 +108,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 地址 = 基地址 + 起始行 × 每行字节数；行数留在设备上</t>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 主机侧打包：地址表与偏移表</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 教程的 grouped GEMM kernel 只发射固定的 NUM_SM 个 CTA，主机不做任何任务分配。每个 CTA 怎样知道自己该算哪些块？这条规则保证了什么，不保证什么？</t>
+          <t xml:space="preserve">Triton 3.7.1 官方教程的 grouped GEMM kernel 只发射固定的 NUM_SM 个 CTA，主机不做任何任务分配。每个 CTA 怎样知道自己该算哪些块？这条规则保证了什么，不保证什么？</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -125,8 +124,7 @@
 • [T#B#扫描]：编号只增不减，问题又按顺序走，所以对问题表顺序走一遍就够；同一个问题里连续领到多块时，用内层循环处理。
 • [T#B#保证]：各 CTA 领到的块数最多差 1。
 • [T#B#不保证]：一块的工作量正比于它的 K 循环次数。边长 1024、512、256、128 的四个方阵、块 128×128×32、84 个 CTA 时，最忙的 CTA 做 36 次 K 循环，最闲的只做 8 次，而整个 kernel 的耗时由最忙的那个决定。
-• [T#B#NUM_SM]：它实际是 CTA 的个数，不必等于物理 SM 数；比总块数还大时，多出来的 CTA 扫一遍什么都领不到。
-[T#B,!c47f17#边界]：各问题的 K 相同时每块工作量相同，这条规则天然均衡；MoE 层就是这种情况。</t>
+[T#B,!c47f17#边界]：各问题的 K 相同时每块工作量相同，只剩块数除不尽带来的最多一块的差距；MoE 层就是这种情况。</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -136,24 +134,24 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 队列、步长 NUM_SM、前缀和；均分块数，不均分工作量</t>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 静态调度、均衡与块大小</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">grouped GEMM 用静态的步长调度。把块从 128×128 缩小到 64×64 后，各 CTA 的工作量更均衡了。这是否意味着更快？以边长 1024、512、256、128 的四个 fp16 方阵、84 个 CTA 为例，说明缩小块换来什么、付出什么。</t>
+          <t xml:space="preserve">Triton 3.7.1 教程的 grouped GEMM 用静态的步长调度，各问题 K 不同时 CTA 的工作量不均衡。把块从 128×128 缩小到 64×64，能让工作量更均衡。这是否意味着更快？请从总耗时由什么决定出发，说明缩小块换来什么、付出什么。</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：不一定。总耗时大致是最忙的 CTA 的工作量乘以做单位工作的耗时：缩小块压低前者，却抬高后者。
-• [T#B#收益有限]：换算成同一单位后，最忙的 CTA 从 36 降到 33，只少 8%；即使完全均衡，也只能降到平均值。
-• [T#B#访存翻倍]：每次乘加摊到的读入量是 1/BN + 1/BM，从 1/64 变成 1/32；整组累计读入从 38.3 MB 变成 76.7 MB。
-• [T#B#固定开销]：块数变多，而每一块都要读地址和行步长、清零累加器、写回结果，这些不随块缩小而等比减少。
-• [T#B#小块的好处]：每个 CTA 占的寄存器和共享内存减半，一个 SM 能同时驻留更多 CTA。
-[T#B,!c47f17#边界]：最终要靠实测：教程把块大小交给 autotune，PyTorch 的 grouped_mm 默认用大块，平均行数或列数不超过 128 时才换小块。上面的数字来自调度模型和编译产物，不是 GPU 计时。</t>
+• [T#B#收益有限]：再均衡，最忙的 CTA 也只能降到平均值。教程示例组（边长 1024、512、256、128 的四个方阵，84 个 CTA）里，换算成同一单位后最忙的 CTA 只从 36 降到 33，约少 8%；这些数字是示意，不必背。
+• [T#B#访存翻倍]：每次乘加摊到的读入量是 1/BM + 1/BN，从 1/64 变成 1/32，读入的总字节数翻倍。
+• [T#B#固定开销]：块数变成原来的 4 倍，每领一块都要再读一次地址和行步长，这部分开销按块数计。
+• [T#B#小块的好处]：每个 CTA 占的寄存器和共享内存减少，一个 SM 能同时驻留更多 CTA。
+[T#B,!c47f17#边界]：最终要靠实测：教程把块大小交给 autotune；PyTorch 2.13 的 grouped_mm 默认用大块，平均行数或列数不超过 128 时才换小块。示例数字来自调度模型，不是 GPU 计时。</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -163,48 +161,48 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 耗时 ≈ 最忙 CTA 的工作量 × 单位工作耗时</t>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 静态调度、均衡与块大小</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">grouped GEMM 按块给 CTA 分配任务。各问题的 K 相差很大时，块数分得再均匀，CTA 的工作量也不均衡。根本原因是什么？有哪两种不缩小块的改进办法，各自的代价是什么？</t>
+          <t xml:space="preserve">grouped GEMM 的静态调度只均分块数，而一块必须由同一个 CTA 做完；各问题的 K 相差很大时，CTA 的工作量就不均衡。在 CUTLASS 3.9.2 里，有哪两种不缩小块的改进办法，各自靠什么改善均衡？</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：根本原因是一块必须由同一个 CTA 做完，K 方向没有被切分；调度均分的是块数，不是工作量。
-• [T#B#按 K 排序]：把问题按 K 从大到小排，同一轮里相邻的块 K 相近。调度模型里 100 个随机尺寸的问题，最忙与平均之比从 1.09–1.27 降到 1.03–1.05，访存量不变。CUTLASS 的示例程序提供这个选项。
-• [T#B#Stream-K]：CUTLASS 的 Stream-K 把所有块的 K 循环总量均分给各 CTA，一块的 K 范围可以切给两个 CTA；代价是两边各算出部分和，需要额外的合并步骤。
-[T#B,!c47f17#边界]：排序的动机是从设计推断的，CUTLASS 源码没有写；Stream-K 快约 1.2 倍的数字来自它的示例自带的样例输出，是厂商数字。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：一是按 K 从大到小给问题排序，让同一轮里相邻的块工作量相近；二是 Stream-K，把 K 循环本身切开，均分的是工作量而不是块数。
+• [T#B#按 K 排序]：CUTLASS 的示例程序提供 --sort-problems 选项。调度模型里 100 个随机尺寸的问题，最忙与平均之比从 1.09–1.27 降到 1.03–1.05，访存量不变。
+• [T#B#Stream-K]：把所有块的 K 循环总量均分给各 CTA，一块的 K 范围可以切给两个 CTA；代价是两边各算出部分和，需要额外的合并步骤。
+[T#B,!c47f17#边界]：排序的动机是从设计推断的，CUTLASS 源码没有写明。</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">一块不可分；排序让相邻块 K 相近，Stream-K 切分 K</t>
+          <t xml:space="preserve">排序让相邻块 K 相近；Stream-K 切分 K 循环，代价是合并部分和</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 一块不可分；排序让相邻块 K 相近，Stream-K 切分 K</t>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 静态调度、均衡与块大小</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">grouped GEMM 的每个 CTA 都要先找出手里的块编号属于哪个问题。Triton 教程用顺序扫描。当问题很多时，例如 256 个专家、每个专家 4 块、128 个 CTA，这种扫描的开销有多大？CUTLASS 3.9.2 用了哪两种办法降低它？</t>
+          <t xml:space="preserve">grouped GEMM 的每个 CTA 都要先找出手里的块编号属于哪个问题，Triton 教程的做法是逐个问题顺序扫描。问题很多时，例如 256 个专家、每个专家 4 块、128 个 CTA，每个 CTA 要扫描多少步？CUTLASS 3.9.2 有哪两种机制不需要这样逐个问题地扫描？</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：扫描的总步数是 CTA 数乘以问题数，和块的计算量无关：这个例子里每个 CTA 要走 256 步，只为领 8 块，连一块都领不到的 CTA 也要走完全表。
 • [T#B#重复执行]：kernel 里的标量代码由 CTA 的每个线程各执行一遍：128 个线程在同一时刻读同一个问题的尺寸、做同一个加法。
-• [T#B#warp 内前缀和]：CUTLASS 让一个 warp 的 32 个线程各读一个不同的问题，再用 warp 内的前缀和得到每个问题的结束编号，一步跨过 32 个问题；同一个例子里每个 CTA 只需 8 步。
-• [T#B#主机预计算]：它的另一种模式由主机把每个 CTA 依次做哪一块算成表，设备上不再扫描。
-[T#B,!c47f17#边界]：问题只有几个时，扫描可以忽略，教程的顺序扫描是合理的。</t>
+• [T#B#warp 内前缀和]：让一个 warp 的 32 个线程各读一个不同的问题，再用 warp 内的前缀和得到每个问题的结束编号，一步跨过 32 个问题；同一个例子里每个 CTA 只需 8 步。
+• [T#B#主机预计算]：另一种模式（kHostPrecompute）由主机把每个 CTA 依次做哪一块算成表，设备上不再扫描。
+[T#B,!c47f17#边界]：说 CUTLASS 是为了降低扫描开销才这样设计，是从设计反推的，CUTLASS 没有这样写。</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -214,14 +212,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 扫描步数 = CTA 数 × 问题数；warp 前缀和或主机预计算</t>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 静态调度、均衡与块大小</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 教程的 grouped GEMM kernel 去掉了所有 mask，假定每个问题的 M、N、K 都是块大小的整数倍。矩阵连续存放时，如果 M、N、K 分别不是整数倍，各会发生什么？哪一种最难被与参考结果比较的测试发现？</t>
+          <t xml:space="preserve">Triton 3.7.1 教程的 grouped GEMM kernel 去掉了所有 mask，假定每个问题的 M、N、K 都是块大小的整数倍。矩阵连续存放时，如果 M、N、K 分别不是整数倍，各会发生什么？哪一种最难被与参考结果比较的测试发现？</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -240,14 +238,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · M：写到 C 之后；N：绕行加竞争写；K：读到别处的数据</t>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 满块假定与三个方向的越界</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">一个 GPU kernel 可能越界读，也可能越界写，但把它的输出和参考实现逐个比较却全部通过。怎样设计测试，让越界读和越界写都必然暴露？</t>
+          <t xml:space="preserve">一个 GPU kernel 可能越界读，也可能越界写，但把它的输出和参考实现逐个比较却全部通过。怎样设计测试，才能可靠地暴露越界写，以及影响到结果的越界读？</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -256,8 +254,8 @@
 • [T#B#越界写]：运行后检查输出四周的保护区是否仍然全是哨兵值。
 • [T#B#越界读]：界外读到的 NaN 只要影响到有效结果，结果就变成 NaN；不这样做，界外恰好是 0 时测试会假通过。
 • [T#B#保护区的大小]：每一侧至少留一整块。块是 128 行而矩阵只有 1 行时，越界可以达到 127 行。
-• [T#B#对接口的要求]：被测函数必须能接收调用方提供的输出张量；视图的行步长大于列数，所以实现里的行步长要取真实的 stride(0)。
-[T#B,!c47f17#边界]：保护区测试要排在普通数值测试之前，让越界写先在保护区里被报告出来。</t>
+• [T#B#对接口的要求]：被测函数必须能接收调用方提供的输出张量，行步长也要取真实的 stride(0)：\[4, 100\] 的张量取 \[:, :64\] 后形状是 (4, 64)、步长是 (100, 1)，用列数代替行步长不会报错，只会读写错位。
+[T#B,!c47f17#边界]：越界超出了保护区，或者越界写入的值恰好等于哨兵值时，这种测试会漏报。</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -267,23 +265,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 输入填 NaN，输出填哨兵值，保护区至少一整块</t>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 满块假定与三个方向的越界；学习者报告的实现问题</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 3.7.1 教程的 grouped GEMM kernel 里，矩阵的指针是运行时从地址表读出来的，随后有一句 tl.multiple_of(a_ptrs, \[16, 16\])。这一句是什么性质的语句？为什么把张量直接当参数的普通 kernel 不用写？去掉它，K 循环里的数据搬运会怎样变化？</t>
+          <t xml:space="preserve">Triton 3.7.1 教程的 grouped GEMM kernel 从地址表读出矩阵指针后，写了一句 tl.multiple_of(a_ptrs, \[16, 16\])；把张量直接当参数传入的普通 kernel 不用写这一句。这一句起什么作用？为什么从表里读出的指针需要它，直接传入的张量却不需要？</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：它是一句不被检查的对齐保证，相当于 C 里的 __builtin_assume_aligned：编译器据此才使用一次搬 16 字节的异步拷贝。
-• [T#B#为什么要写]：张量当参数传入时，Triton 在发射前检查首地址并自动打上对齐标记；从地址表读出的指针，编译器对它一无所知。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：它是一句不被检查的对齐保证，相当于 C 里的 __builtin_assume_aligned：告诉编译器这些地址是 16 的倍数，编译器据此才用一次搬 16 字节的异步拷贝。
+• [T#B#为什么要写]：张量当参数传入时，Triton 在发射前检查首地址是否为 16 的倍数，并按结果特化 kernel；从地址表读出的只是整数，编译器对它的对齐一无所知。
 • [T#B#去掉以后]：退回每次只搬 2 字节的普通读；一次搬的宽度不到 4 字节时 Triton 不做流水，所以连边搬边算也一起失去。
-• [T#B#按指针生效]：保证只作用在写了这一句的指针上。只删掉 B 的那一句时，A 仍用 16 字节的异步拷贝，B 改为逐个元素同步读入。
-[T#B,!c47f17#边界]：保证成立需要首地址和行步长的字节数都是 16 的倍数。不成立时编译器照样生成 16 字节的指令，这是未定义行为，没有任何报错；不写保证则没有这种风险，只是慢。</t>
+[T#B,!c47f17#边界]：编译器和运行时都不检查这项保证。保证不成立属未定义行为：可能触发 misaligned address 之类的异常，也可能静默读错或碰巧正确；不写保证就没有这种风险，只是慢。</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -293,23 +290,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 不被检查的保证；16 字节异步拷贝的前提</t>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 对齐保证、异步拷贝与 TMA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">一个 fp16 矩阵首地址是 16 的倍数，但每行有 100 个元素，即行步长 200 字节。为什么 tl.multiple_of(ptrs, \[16, 16\]) 对它不成立？想继续用异步拷贝，应该怎样写保证？换成 TMA 描述符可以吗？</t>
+          <t xml:space="preserve">在 Triton 3.7.1（NVIDIA GPU）中，一个 fp16 矩阵首地址是 16 的倍数，但每行有 100 个元素，即行步长 200 字节。想让 K 循环继续用异步拷贝，tl.multiple_of 最多能如实写成多少，为什么？换成 TMA 描述符搬这个矩阵，又会怎样？</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：对齐的要求落在每一条拷贝指令上。第 m 行的行首是 首地址 + m × 200 字节，奇数行余 8，不是 16 的倍数；但它们都是 8 的倍数，所以应当如实保证 8。
-• [T#B#降档]：异步拷贝一次可以搬 4、8 或 16 字节。写成 tl.multiple_of(ptrs, \[8, 8\]) 后，编译器改用 8 字节的异步拷贝，指令数是 16 字节时的两倍，流水仍然保留。
-• [T#B#各档对比]：同一个 K 循环在 sm_89 上：保证 16 是 24 条异步拷贝，保证 8 是 48 条，保证 4 是 96 条；不写保证是 64 条 2 字节的普通读，没有流水。
-• [T#B#TMA]：TMA 没有 8 字节的模式。行步长不是 16 字节倍数的矩阵不能直接交给它，只能先改变数据的摆放。
-[T#B,!c47f17#边界]：保证必须如实：能保证多少写多少。写大了是未定义行为，编译器和运行时都不会拦。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：最多如实写 8。对齐的要求落在每一条拷贝指令上：第 m 行的行首是 首地址 + m × 200 字节，奇数行除以 16 余 8，但所有行首都是 8 的倍数。TMA 没有 8 字节这一档，不能直接搬它。
+• [T#B#降档]：异步拷贝一次可以搬 4、8 或 16 字节。写成 tl.multiple_of(ptrs, \[8, 8\]) 后，编译器改用 8 字节的异步拷贝：每条搬的字节减半、条数翻倍，流水仍然保留；不写保证则退回每次 2 字节的普通读，没有流水。
+• [T#B#TMA]：描述符要求行步长的字节数是 16 的倍数，没有降档的余地；行步长 200 字节的矩阵只能先改变数据的摆放，例如拷进一块行步长加宽的缓冲区。
+[T#B,!c47f17#边界]：保证必须如实：能保证多少写多少，写大了就是未定义行为。</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -319,22 +315,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 行首 = 首地址 + m × 行步长；异步拷贝可降档，TMA 不行</t>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 对齐保证、异步拷贝与 TMA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 教程的指针版 grouped GEMM 只给 A、B 的指针写了对齐保证，写回 C 用的是每次 2 字节的普通写。如果给 C 的指针也加上 tl.multiple_of(c_ptrs, \[16, 16\])，写回能变成异步的吗？实际得到什么？</t>
+          <t xml:space="preserve">在 Triton 3.7.1（NVIDIA GPU）中，教程的指针版 grouped GEMM 写回 C 用的是每次 2 字节的普通写。如果给 C 的指针加上 tl.multiple_of(c_ptrs, \[16, 16\])，写回会变成什么样，能不能变成异步的？</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能。异步拷贝指令 cp.async 只有从显存到共享内存一个方向，写回显存仍然是普通的写指令。
-• [T#B#实际收益]：每线程 128 条 2 字节的写变成 16 条 16 字节的写，指令数降到八分之一。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：写回只会变宽，不会变成异步：异步拷贝指令 cp.async 只有从显存到共享内存一个方向，写回显存仍然是普通的写指令。
+• [T#B#实际收益]：每条写从 2 字节变成 16 字节，写指令数降到八分之一。
 • [T#B#异步写回]：从共享内存到显存的异步搬运只存在于 TMA 那一族指令里，需要 sm_90。
-[T#B,!c47f17#边界]：加了保证就要对 C 的对齐负责：保证不成立时同样是未定义行为。</t>
+[T#B,!c47f17#边界]：加了保证就要对 C 的对齐负责：C 的行步长不是 16 字节的倍数时，原本安全的写回会变成未定义行为。</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -344,23 +340,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · cp.async 只做读方向；给 C 加保证只是把写变宽</t>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 对齐保证、异步拷贝与 TMA</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 3.7.1 教程的描述符版 grouped GEMM 在 sm_90 上用 TMA 搬数据。块超出矩阵边界时，它和指针版的处理有什么不同？它解除了指针版的哪个限制，又带来哪些新的要求？在没有 TMA 的设备上它会变成什么？</t>
+          <t xml:space="preserve">Triton 3.7.1 教程的描述符版 grouped GEMM 在 sm_90 上用 TMA 搬数据。块超出矩阵边界时，它怎样处理界外的元素？这让它摆脱了指针版的哪个限制，又换来了哪些新要求？</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：描述符带着矩阵的真实形状，硬件知道哪些元素在界外：读的时候补 0，写的时候不写。所以描述符版不再要求尺寸是块的整数倍，限制换成了对齐。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：描述符带着矩阵的真实形状，硬件知道哪些元素在界外：读的时候补 0，写的时候不写。所以描述符版不再要求尺寸是块的整数倍，100 行的 A、K=1000 都能算对；限制换成了对齐。
 • [T#B#对齐]：行步长的字节数必须是 16 的倍数，而且没有降档的余地。
-• [T#B#现场创建]：形状来自设备上的尺寸表，描述符只能在设备上现场创建；每个 CTA 需要 768 字节的全局暂存区，所以发射前必须先调用 triton.set_allocator。
-• [T#B#没有 TMA 时]：在 sm_89 或 AMD 后端上，Triton 把描述符改写成指针加 mask，mask 由描述符里的形状生成。结果相同，但没有异步拷贝。
-[T#B,!c47f17#边界]：描述符只描述一块已经存在的内存，创建时不搬数据、不补齐；对齐和存放顺序必须在调用前就已经满足。</t>
+• [T#B#现场创建]：问题个数运行时才知道，描述符只能在 kernel 里按问题现场创建；每个 CTA 因此需要一块全局暂存区，发射前必须先调用 triton.set_allocator。
+[T#B,!c47f17#边界]：描述符只描述一块已经存在的内存，创建时不搬数据、不补齐；对齐和 B 的存放方向必须在调用前就已满足。</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -370,7 +365,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 界外读补 0、写不写；限制从整块换成对齐</t>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 对齐保证、异步拷贝与 TMA</t>
         </is>
       </c>
     </row>
@@ -385,8 +380,8 @@
           <t xml:space="preserve">[T#B,!36b59d#结论]：输出还没有数据，补齐只是分配时多留一点空间，不发生拷贝；输入的行步长是既成事实，要改只能把数据拷贝一遍。
 • [T#B#输出]：多分配再切片即可，不必补零。描述符里的形状仍写 500，只把行步长写宽，硬件就只写每行的前 500 列。
 • [T#B#输入]：要新开一块行步长更宽的缓冲区再拷过去。可以只加宽行步长、逻辑上的列数不变，这样不必补零，但拷贝躲不开。
-• [T#B#为什么报错]：替调用方悄悄拷贝会把代价藏起来，grouped 相对逐组调用的优势可能就此消失；报错让调用方自己决定何时拷贝。
-[T#B,!c47f17#边界]：这里要求的是行步长对齐，不是连续：补宽了行步长的输出在 PyTorch 里反而是不连续的张量。</t>
+• [T#B#为什么报错]：悄悄拷贝的代价会藏在调用里，可能抵消 grouped 相对逐组调用的优势；报错把是否拷贝、何时拷贝留给调用方决定。
+[T#B,!c47f17#边界]：“为什么报错”是从行为反推的设计理由，没有核对 PyTorch 的设计说明；能确认的是行为本身：未对齐的输入被拒绝，输出由它自己补宽行步长。</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -396,22 +391,21 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 输出：分配时留宽；输入：只能拷贝</t>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 对齐保证、异步拷贝与 TMA；转置、补齐与预处理</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 教程的描述符版 grouped GEMM 要求 B 按 \[N, K\] 存放。准备数据时写的是 B.T.contiguous()，kernel 里又写了 tl.dot(a, b.T)。这两处转置各自有没有移动数据？只把 B.T 这个视图交给 kernel 为什么不行？</t>
+          <t xml:space="preserve">Triton 3.7.1 教程的描述符版 grouped GEMM 要求 B 按 \[N, K\] 存放。准备数据时写的是 B.T.contiguous()，kernel 里又写了 tl.dot(a, b.T)。这两处转置各自有没有移动数据？只把 B.T 这个视图交给 kernel 为什么不行？</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：主机侧那一次真的拷贝重排了内存，kernel 里那一次不搬任何数据。
-• [T#B#视图]：B.T 和 B 是同一块内存，只是换了读法：\[3, 2\] 的 B 转置后步长变成 (1, 2)，行内不再连续。
-• [T#B#拷贝]：.contiguous() 才新开一块内存，按 \[N, K\] 的行优先顺序把数据排好。
-• [T#B#kernel 里的 b.T]：它作用在已经搬进共享内存的一块上，编译产物里只是给这一块贴上转置的标记，矩阵乘指令按这个顺序去读。
+• [T#B#主机侧]：B.T 只是视图，和 B 是同一块内存，只换了读法：\[3, 2\] 的 B 转置后步长变成 (1, 2)，行内不再连续；.contiguous() 才新开一块内存，按 \[N, K\] 的行优先顺序把数据排好。
+• [T#B#kernel 里的 b.T]：它作用在已经搬进共享内存的一块上；编译产物里只是给这一块贴上 transposed = true 的标签，不搬数据。
 • [T#B#视图为什么不行]：包装函数只传首地址和 stride(0)，视图的 stride(0) 是 1；描述符要求最后一维连续；TMA 把数据原样搬进共享内存，不会重排。
 [T#B,!c47f17#边界]：PyTorch 线性层的权重本来就按 \[输出维, 输入维\] 存，也就是 \[N, K\]，真实系统里通常不需要这次拷贝。</t>
         </is>
@@ -423,7 +417,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · B.T 是视图，.contiguous() 才拷贝，kernel 里的 b.T 只改标记</t>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 转置、补齐与预处理</t>
         </is>
       </c>
     </row>
@@ -438,7 +432,7 @@
           <t xml:space="preserve">[T#B,!36b59d#结论]：三个维度里只有行数 M 是参差的，所以真正要处理的是 M 方向的不满块，以及 256 个问题带来的找任务开销。
 • [T#B#尺寸]：G=256，K=7168，N=2048，对所有专家都相同。N 是 16 个 128，K 是 224 个 32，都是整块；M 是各专家收到的 token 数，可以是任意值。
 • [T#B#对齐]：各矩阵的行步长都是 16 字节的倍数，对齐保证成立。
-• [T#B#均衡]：各问题的 K 相同，每块的工作量相同，按步长分配天然均衡。
+• [T#B#均衡]：各问题的 K 相同，每块的工作量相同；按步长分配只剩块数除不尽带来的最多一块的差距。
 • [T#B#找任务]：每个 CTA 都要扫描 256 个问题，这部分开销需要控制。
 [T#B,!c47f17#边界]：这是训练和预填充的情形。解码时一步只有很少的 token，每个专家只有几行，块和问题的大小就不匹配了。</t>
         </is>
@@ -450,45 +444,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 只有 M 参差；K 相同所以均衡；256 个问题要扫描</t>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 真实规模与综合验收</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">要让 grouped GEMM 的 kernel 支持任意行数 M，读 A 时必须加 mask。有两种写法：只判断这一行是否存在；或者 M、N、K 三个方向都判断。在 Triton 3.7.1 里，这两种写法对 K 循环里的 16 字节异步拷贝各有什么影响？原因是什么？什么场景下第一种就够？</t>
+          <t xml:space="preserve">要让 grouped GEMM 的 kernel 支持任意行数 M，读 A 时必须加 mask；kernel 里各问题的 M、N、K 都是运行时从尺寸表读出的。有两种写法：只判断这一行是否存在；或者 M、N、K 三个方向都判断。在 Triton 3.7.1（NVIDIA GPU）里，这两种写法对 K 循环里的 16 字节异步拷贝各有什么影响，为什么？什么场景下第一种就够？</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：只有行方向的 mask 时，16 字节的异步拷贝保持不变；三个方向都加 mask 后，异步拷贝消失，退回逐个元素的读。
-• [T#B#原因]：一条拷贝指令搬的是同一行里连续的 8 个元素，只能整段跳过。行方向的 mask 对一段里的 8 个元素取值相同；N、K 方向的 mask 可能只挡住一段的一部分，整段跳过就不够用了。
-• [T#B#编译结果]：在 sm_89 和 sm_90 上，没有 mask 和只有行 mask 都是 24 条 16 字节的异步拷贝；三个方向都有 mask 时没有异步拷贝，只有 64 条 2 字节的读。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：只有行方向的 mask 时，16 字节的异步拷贝保持不变；三个方向都加 mask 后，异步拷贝消失，退回每次 2 字节的普通读，也没有流水。
+• [T#B#宽度规则]：Triton 把一段连续元素合成一条拷贝，宽度取“指针连续且对齐的长度”和“mask 沿连续方向保持不变的长度”中较小的那个；每条拷贝只看一个 mask 位，要么整段拷，要么整段跳过补 0。这是 Triton 的规则，cp.async 指令本身可以只拷一段的一部分。
+• [T#B#三向 mask]：N、K 是从表里读出的运行时值，编译器推不出 N、K 方向的 mask 能在几个元素内保持不变，只能按 1 个元素算：宽度 2 字节，不到 cp.async 最小的 4 字节。行方向的 mask 在一行里处处相同，不限制宽度。
 • [T#B#够用的场景]：各问题的 N、K 都是块大小的整数倍、只有行数参差时，行方向的 mask 就够了，MoE 层正是这样。
 [T#B,!c47f17#边界]：够用的条件是 N、K 整块，不是 N、K 为 8 的倍数：后者管的是对齐，是另一件事。</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">一段 8 个元素只能整段跳过；行 mask 保住异步拷贝</t>
+          <t xml:space="preserve">宽度取指针对齐与 mask 恒定长度的较小者；行 mask 保住异步拷贝</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 一段 8 个元素只能整段跳过；行 mask 保住异步拷贝</t>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 真实规模与综合验收</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">要用 Triton 给一个没有 TMA、也没有异步拷贝指令的新加速器后端写 grouped GEMM。官方教程的指针版和描述符版在这个后端上各会变成什么？哪些部分与后端无关？应该优先保证哪些性质？</t>
+          <t xml:space="preserve">要用 Triton 3.7.1 给一个没有 TMA、也没有异步拷贝指令的新加速器后端写 grouped GEMM。照搬官方教程的指针版和描述符版，哪些部分可以原样沿用，哪些取决于这个后端？应该优先保证哪些性质？</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：两个版本都退回同步搬运，描述符版会被改写成指针加 mask；调度、地址表和行方向的 mask 与后端无关，可以原样沿用。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：调度、地址表和行方向的 mask 与后端无关，可以原样沿用；变的是数据搬运：两个版本都只能同步搬运，而描述符版能不能直接用，取决于这个后端的编译器会不会把描述符改写成指针加 mask。
+• [T#B#改写由后端决定]：Triton 3.7.1 里，这一步改写是各后端在 make_ttir 里按条件加入的 pass：NVIDIA 只在 sm_90 以下加入，AMD 只在不支持 TDM 的架构上加入（只在 sm_89 和 gfx942 上验证过）。新后端不加这个 pass，就要自己为描述符操作实现降级。
 • [T#B#优先一]：M 方向的正确性。行数任意时写越界是静默的，出了问题很难查。
 • [T#B#优先二]：各组的行数留在设备上，不读回主机。否则一次发射省下的时间会被同步吃掉。
 • [T#B#其次]：这两条满足之后，再考虑后端有没有类似异步拷贝或整块搬运的能力。
@@ -502,34 +497,34 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 先保 M 方向正确和行数不回主机，再谈搬运方式</t>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 真实规模与综合验收</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">grouped GEMM 的 kernel 只收到五张整数表：三张地址表、一张尺寸表、一张行步长表。如果包装函数漏掉了对 dtype、行内连续性或 num_sm 的检查，kernel 会报错吗？实际会发生什么？这说明检查应该放在哪里，依据什么来定？</t>
+          <t xml:space="preserve">在 Triton 3.7.1 中，grouped GEMM 的 kernel 只收到五张整数表：三张地址表、一张尺寸表、一张行步长表。如果包装函数漏掉了对 dtype、行内连续性或 num_sm 的检查，会发生什么？这说明检查应该放在哪里、依据什么来定？</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：通常不报错，而是照着假定继续算。张量进了表以后只剩首地址、M、N、K 和行步长，dtype、连续性、设备和对齐这些信息 kernel 没有办法验证。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：包装函数是最后一个能做检查的地方：张量进了表只剩首地址、M、N、K 和行步长，kernel 验证不了 dtype、连续性、设备和对齐，漏掉检查时通常不报错，而是照着假定继续算。所以每项检查都应当对应 kernel 的一条假定。
 • [T#B#dtype]：把 fp32 的 A 交给按 fp16 读的 kernel：结果含 NaN，没有异常。
 • [T#B#行内连续]：把每隔一列取一个元素的视图交进去：kernel 仍按相邻的列去读，绝大部分元素不对，没有异常。
 • [T#B#num_sm]：取 0 或负数时一个 CTA 都不发射，输出从未被写入，也没有异常。
 • [T#B#少数例外]：块大小取 48，或 K 方向的块取 8 时，编译才会报错。
-[T#B,!c47f17#边界]：所以包装函数是最后一个能做检查的地方，每项检查背后都应当有一条 kernel 的假定；没有假定的检查只会拒绝本来能正确处理的输入。</t>
+[T#B,!c47f17#边界]：没有对应假定的检查只会拒绝本来能正确处理的输入。上面的现象是在 CPU 解释器上删去检查后实测的。</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">表里只有整数；检查漏掉时静默算错</t>
+          <t xml:space="preserve">包装函数是最后的检查点；检查漏掉时静默算错；每项检查对应一条假定</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 表里只有整数；检查漏掉时静默算错</t>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · A6：每项检查保护哪个假定</t>
         </is>
       </c>
     </row>
@@ -554,32 +549,105 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 循环变量类型不变；原地改写会累加偏移</t>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 学习者报告的实现问题</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">把一个二维张量交给按 首地址 + 行 × 行步长 + 列 寻址的 kernel 时，行步长应该从哪里取？如果图省事用列数代替，什么样的输入会出错，出错时是什么现象？</t>
+          <t xml:space="preserve">Triton 3.7.1 教程的描述符版 grouped GEMM 在 sm_90 上用 TMA 写回结果，而且只发射固定数量的 CTA，每个 CTA 循环领取多块。与每块一个 CTA 的写法相比，这种结构给写回带来了什么机会？</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：取 tensor.stride(0)，不能用列数代替；两者只在张量连续存放时相等。
-• [T#B#反例]：\[4, 100\] 的张量取切片 \[:, :64\]，形状是 (4, 64)，步长却是 (100, 1)：相邻两行相隔 100 个元素。
-• [T#B#现象]：用列数当行步长不会报错，只是从第 1 行起读到错位的数据，结果错。
-[T#B,!c47f17#边界]：所以测试里要有行步长不等于列数的输入，例如嵌在更大缓冲区里的视图，或同一个张量的多个切片。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：第 i 块的写回可以和第 i+1 块的计算重叠：发起写回后不等它完成，直接去领下一块。每块一个 CTA 时，这个 CTA 写完就结束了，自己没有下一块可以和写回重叠。
+• [T#B#每块的顺序]：先等上一块的写回完成，把这一块的结果写进共享内存，发起从共享内存到显存的 TMA 搬运后不等待，接着领下一块、开始它的读和计算。
+• [T#B#为什么要 TMA]：从共享内存到显存的异步搬运属于 TMA 那一族指令，需要 sm_90；异步拷贝指令 cp.async 只有从显存到共享内存一个方向。
+[T#B,!c47f17#边界]：描述符版没有在有 TMA 的设备上运行过，重叠带来的实际收益没有测量。</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">行步长取 stride(0)；视图的步长不等于列数</t>
+          <t xml:space="preserve">发起写回不等待，接着算下一块；只算一块的 CTA 没有可重叠的</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 行步长取 stride(0)；视图的步长不等于列数</t>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 对齐保证、异步拷贝与 TMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一个 MoE 算子约定：设备上的偏移表 offs 不得读回主机。在 PyTorch 2.13 的测试里，怎样让任何读回 offs 的代码当场失败？这种检查拦不住什么？</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：传入一个 torch.Tensor 的子类代替 offs，让所有把数据读回主机的调用都抛 AssertionError，设备上的运算照常进行。
+• [T#B#拦哪些调用]：.cpu()、.item()、.tolist()、.numpy()、int()、bool()；直接打印也会失败，因为打印张量内部会调用 .tolist()。
+• [T#B#为什么要禁止]：读回主机时，主机必须等 GPU 把排在前面的工作做完；PyTorch 的回退路径正是先 offs.cpu() 再逐组循环。
+[T#B,!c47f17#边界]：它只拦住对这个对象本身的读回：数据先转存到普通张量再读回，就拦不住。</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">读回调用会抛 AssertionError 的张量子类；拦不住转存后的读回</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 练习：提交、定位与测试缺口</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grouped GEMM 的包装函数要为整组问题选一个特化标志：只有每个问题的 N、K 都是块大小的整数倍时，才能选只加行方向 mask 的快路径。首版在遍历问题的循环结束后，用循环变量里剩下的 N、K 来判断；验收测试里有含不整块问题的混合组，却全部通过。为什么没测出来？测试输入应该怎样设计？</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：因为原有的混合组里，不整块的问题恰好都排在最后：循环结束后残留的正是它的 N、K，标志碰巧选对了。测试要把特殊问题分别放在最前、中间和最后。
+• [T#B#漏掉的情形]：不整块的问题排在整块问题前面时，整组被当成满块处理：它的结果含 NaN，输出的保护区被改写。
+• [T#B#正确写法]：标志由整组共同决定：遍历所有问题，只要有一个问题的 N 或 K 不是整块，就选三个方向都加 mask 的通用路径。
+[T#B,!c47f17#边界]：一个量由整组共同决定时，测试都要变换特殊元素的位置；特殊元素只放在末尾，会漏掉“只看最后一个”这类错误。</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">残留的循环变量只代表最后一个；特殊问题放在最前、中间、最后</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 练习：提交、定位与测试缺口</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在 Triton 3.7.1 的 kernel 里构造二维 mask 时写成 a &lt; M &amp; b &lt; K，报错 simultaneous multiple comparison is not supported。Python 把这个表达式解析成了什么，应该怎样写？</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：Python 里 &amp; 的优先级高于 &lt;，表达式被解析成链式比较 a &lt; (M &amp; b) &lt; K，Triton 不支持这种链式比较。每个比较都要加括号：(a &lt; M) &amp; (b &lt; K)。
+[T#B,!c47f17#边界]：这条优先级规则来自 Python 本身，在 NumPy 和 PyTorch 里相同，不是 Triton 特有的。</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp; 优先级高于比较，变成链式比较；每个比较加括号</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grouped GEMM 学习记录 10-09 · 学习者报告的实现问题</t>
         </is>
       </c>
     </row>

--- a/docs/triton-learning/cards/triton-lesson-08-grouped-gemm-technical-qa.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-08-grouped-gemm-technical-qa.xlsx
@@ -280,7 +280,7 @@
           <t xml:space="preserve">[T#B,!36b59d#结论]：它是一句不被检查的对齐保证，相当于 C 里的 __builtin_assume_aligned：告诉编译器这些地址是 16 的倍数，编译器据此才用一次搬 16 字节的异步拷贝。
 • [T#B#为什么要写]：张量当参数传入时，Triton 在发射前检查首地址是否为 16 的倍数，并按结果特化 kernel；从地址表读出的只是整数，编译器对它的对齐一无所知。
 • [T#B#去掉以后]：退回每次只搬 2 字节的普通读；一次搬的宽度不到 4 字节时 Triton 不做流水，所以连边搬边算也一起失去。
-[T#B,!c47f17#边界]：编译器和运行时都不检查这项保证。保证不成立属未定义行为：可能触发 misaligned address 之类的异常，也可能静默读错或碰巧正确；不写保证就没有这种风险，只是慢。</t>
+[T#B,!c47f17#边界]：编译器和运行时都不检查这项保证。保证不成立属未定义行为：H100 上实测（Triton 3.7.1 与 3.8.0），首地址偏 2 字节或奇数行偏 8 字节都报 misaligned address，此后整个进程的 CUDA 都不能再用；其他后端未实测。不写保证就没有这种风险，只是慢。</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
